--- a/procesos/importarFacturacion/inputs/tramites/Facturado a 07072026 - CR.xlsx
+++ b/procesos/importarFacturacion/inputs/tramites/Facturado a 07072026 - CR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rolaboral1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\importarFacturacion\inputs\tramites\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBC52DF-562B-4BD0-927B-6B5E1D3733B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD726FD6-F79A-4A90-8029-7B5ACBF5B55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CE941F5-1ABC-4A4F-8012-067F58F11DCD}"/>
+    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{5CE941F5-1ABC-4A4F-8012-067F58F11DCD}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIOS" sheetId="1" r:id="rId1"/>
@@ -1365,9 +1365,6 @@
           <cell r="B1" t="str">
             <v>COD</v>
           </cell>
-          <cell r="C1" t="str">
-            <v>Importe</v>
-          </cell>
         </row>
         <row r="2">
           <cell r="A2" t="str">
@@ -1376,9 +1373,6 @@
           <cell r="B2" t="str">
             <v>0.001</v>
           </cell>
-          <cell r="C2" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
@@ -1395,9 +1389,6 @@
           <cell r="B4" t="str">
             <v>0.003</v>
           </cell>
-          <cell r="C4">
-            <v>30</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="A5" t="str">
@@ -1406,9 +1397,6 @@
           <cell r="B5" t="str">
             <v>0.005</v>
           </cell>
-          <cell r="C5">
-            <v>31</v>
-          </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
@@ -1449,9 +1437,6 @@
           <cell r="B10" t="str">
             <v>0.010</v>
           </cell>
-          <cell r="C10">
-            <v>23</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
@@ -1468,9 +1453,6 @@
           <cell r="B12" t="str">
             <v>0.012</v>
           </cell>
-          <cell r="C12">
-            <v>40</v>
-          </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
@@ -1479,9 +1461,6 @@
           <cell r="B13" t="str">
             <v>0.013</v>
           </cell>
-          <cell r="C13">
-            <v>40</v>
-          </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
@@ -1490,9 +1469,6 @@
           <cell r="B14" t="str">
             <v>0.014</v>
           </cell>
-          <cell r="C14">
-            <v>40</v>
-          </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
@@ -1501,9 +1477,6 @@
           <cell r="B15" t="str">
             <v>0.015</v>
           </cell>
-          <cell r="C15">
-            <v>40</v>
-          </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
@@ -1512,9 +1485,6 @@
           <cell r="B16" t="str">
             <v>0.016</v>
           </cell>
-          <cell r="C16">
-            <v>40</v>
-          </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
@@ -1523,9 +1493,6 @@
           <cell r="B17" t="str">
             <v>0.017</v>
           </cell>
-          <cell r="C17">
-            <v>40</v>
-          </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
@@ -1534,9 +1501,6 @@
           <cell r="B18" t="str">
             <v>0.018</v>
           </cell>
-          <cell r="C18">
-            <v>40</v>
-          </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
@@ -1545,9 +1509,6 @@
           <cell r="B19" t="str">
             <v>0.019</v>
           </cell>
-          <cell r="C19">
-            <v>40</v>
-          </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
@@ -1556,9 +1517,6 @@
           <cell r="B20" t="str">
             <v>0.020</v>
           </cell>
-          <cell r="C20">
-            <v>40</v>
-          </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
@@ -1567,9 +1525,6 @@
           <cell r="B21" t="str">
             <v>0.021</v>
           </cell>
-          <cell r="C21">
-            <v>23</v>
-          </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
@@ -1578,9 +1533,6 @@
           <cell r="B22" t="str">
             <v>0.022</v>
           </cell>
-          <cell r="C22">
-            <v>9</v>
-          </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
@@ -1589,9 +1541,6 @@
           <cell r="B23" t="str">
             <v>0.023</v>
           </cell>
-          <cell r="C23">
-            <v>9</v>
-          </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
@@ -1600,9 +1549,6 @@
           <cell r="B24" t="str">
             <v>0.025</v>
           </cell>
-          <cell r="C24">
-            <v>40</v>
-          </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
@@ -1611,9 +1557,6 @@
           <cell r="B25" t="str">
             <v>0.027</v>
           </cell>
-          <cell r="C25">
-            <v>26</v>
-          </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
@@ -1622,9 +1565,6 @@
           <cell r="B26" t="str">
             <v>0.029</v>
           </cell>
-          <cell r="C26">
-            <v>15</v>
-          </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
@@ -1633,9 +1573,6 @@
           <cell r="B27" t="str">
             <v>0.037</v>
           </cell>
-          <cell r="C27">
-            <v>23</v>
-          </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
@@ -1644,9 +1581,6 @@
           <cell r="B28" t="str">
             <v>0.038</v>
           </cell>
-          <cell r="C28">
-            <v>33</v>
-          </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
@@ -1655,9 +1589,6 @@
           <cell r="B29" t="str">
             <v>0.039</v>
           </cell>
-          <cell r="C29">
-            <v>44</v>
-          </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
@@ -1666,9 +1597,6 @@
           <cell r="B30" t="str">
             <v>0.040</v>
           </cell>
-          <cell r="C30">
-            <v>55</v>
-          </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
@@ -1677,9 +1605,6 @@
           <cell r="B31" t="str">
             <v>0.041</v>
           </cell>
-          <cell r="C31">
-            <v>65</v>
-          </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
@@ -1688,9 +1613,6 @@
           <cell r="B32" t="str">
             <v>0.042</v>
           </cell>
-          <cell r="C32">
-            <v>76</v>
-          </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
@@ -1699,9 +1621,6 @@
           <cell r="B33" t="str">
             <v>0.043</v>
           </cell>
-          <cell r="C33">
-            <v>87</v>
-          </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
@@ -1710,9 +1629,6 @@
           <cell r="B34" t="str">
             <v>0.044</v>
           </cell>
-          <cell r="C34">
-            <v>98</v>
-          </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
@@ -1721,9 +1637,6 @@
           <cell r="B35" t="str">
             <v>0.045</v>
           </cell>
-          <cell r="C35">
-            <v>109</v>
-          </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
@@ -1732,9 +1645,6 @@
           <cell r="B36" t="str">
             <v>0.046</v>
           </cell>
-          <cell r="C36">
-            <v>130</v>
-          </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
@@ -1743,9 +1653,6 @@
           <cell r="B37" t="str">
             <v>0.047</v>
           </cell>
-          <cell r="C37">
-            <v>152</v>
-          </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
@@ -1754,9 +1661,6 @@
           <cell r="B38" t="str">
             <v>0.048</v>
           </cell>
-          <cell r="C38">
-            <v>173</v>
-          </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
@@ -1765,9 +1669,6 @@
           <cell r="B39" t="str">
             <v>0.057</v>
           </cell>
-          <cell r="C39">
-            <v>9</v>
-          </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
@@ -1784,9 +1685,6 @@
           <cell r="B41" t="str">
             <v>0.060</v>
           </cell>
-          <cell r="C41">
-            <v>30</v>
-          </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
@@ -1795,9 +1693,6 @@
           <cell r="B42" t="str">
             <v>0.066</v>
           </cell>
-          <cell r="C42" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
@@ -1806,9 +1701,6 @@
           <cell r="B43" t="str">
             <v>0.067</v>
           </cell>
-          <cell r="C43">
-            <v>40</v>
-          </cell>
         </row>
         <row r="44">
           <cell r="A44" t="str">
@@ -1816,9 +1708,6 @@
           </cell>
           <cell r="B44" t="str">
             <v>0.068</v>
-          </cell>
-          <cell r="C44">
-            <v>386</v>
           </cell>
         </row>
         <row r="45">
@@ -1829,9 +1718,6 @@
           <cell r="B45" t="str">
             <v>0.069</v>
           </cell>
-          <cell r="C45">
-            <v>298</v>
-          </cell>
         </row>
         <row r="46">
           <cell r="A46" t="str">
@@ -1840,9 +1726,6 @@
           <cell r="B46" t="str">
             <v>0.070</v>
           </cell>
-          <cell r="C46">
-            <v>57</v>
-          </cell>
         </row>
         <row r="47">
           <cell r="A47" t="str">
@@ -1851,9 +1734,6 @@
           <cell r="B47" t="str">
             <v>0.071</v>
           </cell>
-          <cell r="C47">
-            <v>57</v>
-          </cell>
         </row>
         <row r="48">
           <cell r="A48" t="str">
@@ -1862,9 +1742,6 @@
           <cell r="B48" t="str">
             <v>0.072</v>
           </cell>
-          <cell r="C48">
-            <v>26</v>
-          </cell>
         </row>
         <row r="49">
           <cell r="A49" t="str">
@@ -1872,9 +1749,6 @@
           </cell>
           <cell r="B49" t="str">
             <v>0.073</v>
-          </cell>
-          <cell r="C49">
-            <v>46</v>
           </cell>
         </row>
         <row r="50">
@@ -1888,9 +1762,6 @@
           <cell r="B50" t="str">
             <v>0.075</v>
           </cell>
-          <cell r="C50">
-            <v>360</v>
-          </cell>
         </row>
         <row r="51">
           <cell r="A51" t="str">
@@ -1899,9 +1770,6 @@
           <cell r="B51" t="str">
             <v>0.076</v>
           </cell>
-          <cell r="C51">
-            <v>40</v>
-          </cell>
         </row>
         <row r="52">
           <cell r="A52" t="str">
@@ -1910,9 +1778,6 @@
           <cell r="B52" t="str">
             <v>0.077</v>
           </cell>
-          <cell r="C52">
-            <v>46</v>
-          </cell>
         </row>
         <row r="53">
           <cell r="A53" t="str">
@@ -1921,9 +1786,6 @@
           <cell r="B53" t="str">
             <v>0.080</v>
           </cell>
-          <cell r="C53">
-            <v>54</v>
-          </cell>
         </row>
         <row r="54">
           <cell r="A54" t="str">
@@ -1932,9 +1794,6 @@
           <cell r="B54" t="str">
             <v>0.081</v>
           </cell>
-          <cell r="C54">
-            <v>30</v>
-          </cell>
         </row>
         <row r="55">
           <cell r="A55" t="str">
@@ -1943,9 +1802,6 @@
           <cell r="B55" t="str">
             <v>0.082</v>
           </cell>
-          <cell r="C55">
-            <v>23</v>
-          </cell>
         </row>
         <row r="56">
           <cell r="A56" t="str">
@@ -1954,9 +1810,6 @@
           <cell r="B56" t="str">
             <v>0.083</v>
           </cell>
-          <cell r="C56">
-            <v>46</v>
-          </cell>
         </row>
         <row r="57">
           <cell r="A57" t="str">
@@ -1965,9 +1818,6 @@
           <cell r="B57" t="str">
             <v>0.084</v>
           </cell>
-          <cell r="C57">
-            <v>55</v>
-          </cell>
         </row>
         <row r="58">
           <cell r="A58" t="str">
@@ -1984,9 +1834,6 @@
           <cell r="B59" t="str">
             <v>0.086</v>
           </cell>
-          <cell r="C59">
-            <v>40</v>
-          </cell>
         </row>
         <row r="60">
           <cell r="A60" t="str">
@@ -1995,9 +1842,6 @@
           <cell r="B60" t="str">
             <v>0.087</v>
           </cell>
-          <cell r="C60">
-            <v>40</v>
-          </cell>
         </row>
         <row r="61">
           <cell r="A61" t="str">
@@ -2006,9 +1850,6 @@
           <cell r="B61" t="str">
             <v>0.088</v>
           </cell>
-          <cell r="C61">
-            <v>40</v>
-          </cell>
         </row>
         <row r="62">
           <cell r="A62" t="str">
@@ -2017,9 +1858,6 @@
           <cell r="B62" t="str">
             <v>0.089</v>
           </cell>
-          <cell r="C62">
-            <v>40</v>
-          </cell>
         </row>
         <row r="63">
           <cell r="A63" t="str">
@@ -2028,9 +1866,6 @@
           <cell r="B63" t="str">
             <v>0.090</v>
           </cell>
-          <cell r="C63">
-            <v>40</v>
-          </cell>
         </row>
         <row r="64">
           <cell r="A64" t="str">
@@ -2039,9 +1874,6 @@
           <cell r="B64" t="str">
             <v>0.091</v>
           </cell>
-          <cell r="C64">
-            <v>40</v>
-          </cell>
         </row>
         <row r="65">
           <cell r="A65" t="str">
@@ -2050,9 +1882,6 @@
           <cell r="B65" t="str">
             <v>0.092</v>
           </cell>
-          <cell r="C65">
-            <v>65</v>
-          </cell>
         </row>
         <row r="66">
           <cell r="A66" t="str">
@@ -2061,9 +1890,6 @@
           <cell r="B66" t="str">
             <v>0.093</v>
           </cell>
-          <cell r="C66">
-            <v>62</v>
-          </cell>
         </row>
         <row r="67">
           <cell r="A67" t="str">
@@ -2088,9 +1914,6 @@
           <cell r="B69" t="str">
             <v>0.100</v>
           </cell>
-          <cell r="C69" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="70">
           <cell r="A70" t="str">
@@ -2099,9 +1922,6 @@
           <cell r="B70" t="str">
             <v>0.112</v>
           </cell>
-          <cell r="C70">
-            <v>10</v>
-          </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
@@ -2110,9 +1930,6 @@
           <cell r="B71" t="str">
             <v>0.115</v>
           </cell>
-          <cell r="C71">
-            <v>40</v>
-          </cell>
         </row>
         <row r="72">
           <cell r="A72" t="str">
@@ -2121,9 +1938,6 @@
           <cell r="B72" t="str">
             <v>0.117</v>
           </cell>
-          <cell r="C72">
-            <v>28</v>
-          </cell>
         </row>
         <row r="73">
           <cell r="A73" t="str">
@@ -2132,9 +1946,6 @@
           <cell r="B73" t="str">
             <v>0.118</v>
           </cell>
-          <cell r="C73">
-            <v>12</v>
-          </cell>
         </row>
         <row r="74">
           <cell r="A74" t="str">
@@ -2143,9 +1954,6 @@
           <cell r="B74" t="str">
             <v>0.121</v>
           </cell>
-          <cell r="C74">
-            <v>40</v>
-          </cell>
         </row>
         <row r="75">
           <cell r="A75" t="str">
@@ -2154,9 +1962,6 @@
           <cell r="B75" t="str">
             <v>0.122</v>
           </cell>
-          <cell r="C75">
-            <v>40</v>
-          </cell>
         </row>
         <row r="76">
           <cell r="A76" t="str">
@@ -2165,9 +1970,6 @@
           <cell r="B76" t="str">
             <v>0.123</v>
           </cell>
-          <cell r="C76">
-            <v>40</v>
-          </cell>
         </row>
         <row r="77">
           <cell r="A77" t="str">
@@ -2176,9 +1978,6 @@
           <cell r="B77" t="str">
             <v>0.143</v>
           </cell>
-          <cell r="C77">
-            <v>57</v>
-          </cell>
         </row>
         <row r="78">
           <cell r="A78" t="str">
@@ -2187,9 +1986,6 @@
           <cell r="B78" t="str">
             <v>0.175</v>
           </cell>
-          <cell r="C78">
-            <v>304</v>
-          </cell>
         </row>
         <row r="79">
           <cell r="A79" t="str">
@@ -2206,9 +2002,6 @@
           <cell r="B80" t="str">
             <v>0.201</v>
           </cell>
-          <cell r="C80">
-            <v>131</v>
-          </cell>
         </row>
         <row r="81">
           <cell r="A81" t="str">
@@ -2217,9 +2010,6 @@
           <cell r="B81" t="str">
             <v>0.202</v>
           </cell>
-          <cell r="C81">
-            <v>122</v>
-          </cell>
         </row>
         <row r="82">
           <cell r="A82" t="str">
@@ -2236,9 +2026,6 @@
           <cell r="B83" t="str">
             <v>0.204</v>
           </cell>
-          <cell r="C83">
-            <v>114</v>
-          </cell>
         </row>
         <row r="84">
           <cell r="A84" t="str">
@@ -2247,9 +2034,6 @@
           <cell r="B84" t="str">
             <v>0.218</v>
           </cell>
-          <cell r="C84">
-            <v>40</v>
-          </cell>
         </row>
         <row r="85">
           <cell r="A85" t="str">
@@ -2266,9 +2050,6 @@
           <cell r="B86" t="str">
             <v>0.221</v>
           </cell>
-          <cell r="C86">
-            <v>23</v>
-          </cell>
         </row>
         <row r="87">
           <cell r="A87" t="str">
@@ -2277,9 +2058,6 @@
           <cell r="B87" t="str">
             <v>0.222</v>
           </cell>
-          <cell r="C87">
-            <v>45</v>
-          </cell>
         </row>
         <row r="88">
           <cell r="A88" t="str">
@@ -2288,9 +2066,6 @@
           <cell r="B88" t="str">
             <v>0.223</v>
           </cell>
-          <cell r="C88">
-            <v>40</v>
-          </cell>
         </row>
         <row r="89">
           <cell r="A89" t="str">
@@ -2299,9 +2074,6 @@
           <cell r="B89" t="str">
             <v>0.224</v>
           </cell>
-          <cell r="C89">
-            <v>21</v>
-          </cell>
         </row>
         <row r="90">
           <cell r="A90" t="str">
@@ -2310,9 +2082,6 @@
           <cell r="B90" t="str">
             <v>0.225</v>
           </cell>
-          <cell r="C90">
-            <v>6</v>
-          </cell>
         </row>
         <row r="91">
           <cell r="A91" t="str">
@@ -2321,9 +2090,6 @@
           <cell r="B91" t="str">
             <v>0.238</v>
           </cell>
-          <cell r="C91">
-            <v>57</v>
-          </cell>
         </row>
         <row r="92">
           <cell r="A92" t="str">
@@ -2332,9 +2098,6 @@
           <cell r="B92" t="str">
             <v>0.250</v>
           </cell>
-          <cell r="C92">
-            <v>30</v>
-          </cell>
         </row>
         <row r="93">
           <cell r="A93" t="str">
@@ -2343,9 +2106,6 @@
           <cell r="B93" t="str">
             <v>0.251</v>
           </cell>
-          <cell r="C93">
-            <v>25</v>
-          </cell>
         </row>
         <row r="94">
           <cell r="A94" t="str">
@@ -2354,9 +2114,6 @@
           <cell r="B94" t="str">
             <v>0.260</v>
           </cell>
-          <cell r="C94" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="95">
           <cell r="A95" t="str">
@@ -2364,9 +2121,6 @@
           </cell>
           <cell r="B95" t="str">
             <v>0.261</v>
-          </cell>
-          <cell r="C95" t="str">
-            <v>ESCALADO</v>
           </cell>
         </row>
         <row r="96">
@@ -2402,9 +2156,6 @@
           <cell r="B97" t="str">
             <v>0.302</v>
           </cell>
-          <cell r="C97">
-            <v>42</v>
-          </cell>
         </row>
         <row r="98">
           <cell r="A98" t="str">
@@ -2421,9 +2172,6 @@
           <cell r="B99" t="str">
             <v>1.002</v>
           </cell>
-          <cell r="C99">
-            <v>47</v>
-          </cell>
         </row>
         <row r="100">
           <cell r="A100" t="str">
@@ -2432,9 +2180,6 @@
           <cell r="B100" t="str">
             <v>1.004</v>
           </cell>
-          <cell r="C100">
-            <v>53</v>
-          </cell>
         </row>
         <row r="101">
           <cell r="A101" t="str">
@@ -2442,9 +2187,6 @@
           </cell>
           <cell r="B101" t="str">
             <v>1.005</v>
-          </cell>
-          <cell r="C101">
-            <v>23</v>
           </cell>
         </row>
         <row r="102">
@@ -2460,9 +2202,6 @@
           <cell r="B102" t="str">
             <v>1.006</v>
           </cell>
-          <cell r="C102">
-            <v>209</v>
-          </cell>
         </row>
         <row r="103">
           <cell r="A103" t="str">
@@ -2482,9 +2221,6 @@
           <cell r="B104" t="str">
             <v>1.011</v>
           </cell>
-          <cell r="C104">
-            <v>26</v>
-          </cell>
         </row>
         <row r="105">
           <cell r="A105" t="str">
@@ -2501,9 +2237,6 @@
           <cell r="B106" t="str">
             <v>1.013</v>
           </cell>
-          <cell r="C106">
-            <v>46</v>
-          </cell>
         </row>
         <row r="107">
           <cell r="A107" t="str">
@@ -2520,9 +2253,6 @@
           <cell r="B108" t="str">
             <v>1.017</v>
           </cell>
-          <cell r="C108">
-            <v>53</v>
-          </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -2530,9 +2260,6 @@
           </cell>
           <cell r="B109" t="str">
             <v>1.019</v>
-          </cell>
-          <cell r="C109">
-            <v>36</v>
           </cell>
         </row>
         <row r="110">
@@ -2557,9 +2284,6 @@
           <cell r="B111" t="str">
             <v>1.023</v>
           </cell>
-          <cell r="C111">
-            <v>233</v>
-          </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
@@ -2572,9 +2296,6 @@
           <cell r="B112" t="str">
             <v>1.024</v>
           </cell>
-          <cell r="C112">
-            <v>111</v>
-          </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -2582,9 +2303,6 @@
           </cell>
           <cell r="B113" t="str">
             <v>1.025</v>
-          </cell>
-          <cell r="C113">
-            <v>23</v>
           </cell>
         </row>
         <row r="114">
@@ -2597,9 +2315,6 @@
           <cell r="B114" t="str">
             <v>1.030</v>
           </cell>
-          <cell r="C114">
-            <v>112</v>
-          </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
@@ -2607,9 +2322,6 @@
           </cell>
           <cell r="B115" t="str">
             <v>1.031</v>
-          </cell>
-          <cell r="C115">
-            <v>30</v>
           </cell>
         </row>
         <row r="116">
@@ -2622,9 +2334,6 @@
           <cell r="B116" t="str">
             <v>1.032</v>
           </cell>
-          <cell r="C116">
-            <v>103</v>
-          </cell>
         </row>
         <row r="117">
           <cell r="A117" t="str">
@@ -2633,9 +2342,6 @@
           <cell r="B117" t="str">
             <v>1.034</v>
           </cell>
-          <cell r="C117">
-            <v>77</v>
-          </cell>
         </row>
         <row r="118">
           <cell r="A118" t="str">
@@ -2644,9 +2350,6 @@
           <cell r="B118" t="str">
             <v>1.035</v>
           </cell>
-          <cell r="C118">
-            <v>128</v>
-          </cell>
         </row>
         <row r="119">
           <cell r="A119" t="str">
@@ -2663,9 +2366,6 @@
           <cell r="B120" t="str">
             <v>1.037</v>
           </cell>
-          <cell r="C120">
-            <v>45</v>
-          </cell>
         </row>
         <row r="121">
           <cell r="A121" t="str">
@@ -2674,9 +2374,6 @@
           <cell r="B121" t="str">
             <v>1.038</v>
           </cell>
-          <cell r="C121">
-            <v>77</v>
-          </cell>
         </row>
         <row r="122">
           <cell r="A122" t="str">
@@ -2685,9 +2382,6 @@
           <cell r="B122" t="str">
             <v>1.039</v>
           </cell>
-          <cell r="C122">
-            <v>100</v>
-          </cell>
         </row>
         <row r="123">
           <cell r="A123" t="str">
@@ -2696,9 +2390,6 @@
           <cell r="B123" t="str">
             <v>1.040</v>
           </cell>
-          <cell r="C123">
-            <v>105</v>
-          </cell>
         </row>
         <row r="124">
           <cell r="A124" t="str">
@@ -2707,9 +2398,6 @@
           <cell r="B124" t="str">
             <v>1.041</v>
           </cell>
-          <cell r="C124">
-            <v>135</v>
-          </cell>
         </row>
         <row r="125">
           <cell r="A125" t="str">
@@ -2718,9 +2406,6 @@
           <cell r="B125" t="str">
             <v>1.042</v>
           </cell>
-          <cell r="C125">
-            <v>42</v>
-          </cell>
         </row>
         <row r="126">
           <cell r="A126" t="str">
@@ -2729,9 +2414,6 @@
           <cell r="B126" t="str">
             <v>1.043</v>
           </cell>
-          <cell r="C126">
-            <v>58</v>
-          </cell>
         </row>
         <row r="127">
           <cell r="A127" t="str">
@@ -2740,9 +2422,6 @@
           <cell r="B127" t="str">
             <v>1.044</v>
           </cell>
-          <cell r="C127">
-            <v>79</v>
-          </cell>
         </row>
         <row r="128">
           <cell r="A128" t="str">
@@ -2759,9 +2438,6 @@
           <cell r="B129" t="str">
             <v>1.046</v>
           </cell>
-          <cell r="C129">
-            <v>125</v>
-          </cell>
         </row>
         <row r="130">
           <cell r="A130" t="str">
@@ -2770,9 +2446,6 @@
           <cell r="B130" t="str">
             <v>1.047</v>
           </cell>
-          <cell r="C130">
-            <v>16</v>
-          </cell>
         </row>
         <row r="131">
           <cell r="A131" t="str">
@@ -2781,9 +2454,6 @@
           <cell r="B131" t="str">
             <v>1.048</v>
           </cell>
-          <cell r="C131">
-            <v>77</v>
-          </cell>
         </row>
         <row r="132">
           <cell r="A132" t="str">
@@ -2800,9 +2470,6 @@
           <cell r="B133" t="str">
             <v>1.057</v>
           </cell>
-          <cell r="C133">
-            <v>8</v>
-          </cell>
         </row>
         <row r="134">
           <cell r="A134" t="str">
@@ -2819,9 +2486,6 @@
           <cell r="B135" t="str">
             <v>1.059</v>
           </cell>
-          <cell r="C135">
-            <v>25</v>
-          </cell>
         </row>
         <row r="136">
           <cell r="A136" t="str">
@@ -2830,9 +2494,6 @@
           <cell r="B136" t="str">
             <v>1.079</v>
           </cell>
-          <cell r="C136">
-            <v>40</v>
-          </cell>
         </row>
         <row r="137">
           <cell r="A137" t="str">
@@ -2841,9 +2502,6 @@
           <cell r="B137" t="str">
             <v>1.080</v>
           </cell>
-          <cell r="C137">
-            <v>42</v>
-          </cell>
         </row>
         <row r="138">
           <cell r="A138" t="str">
@@ -2852,9 +2510,6 @@
           <cell r="B138" t="str">
             <v>1.082</v>
           </cell>
-          <cell r="C138">
-            <v>36</v>
-          </cell>
         </row>
         <row r="139">
           <cell r="A139" t="str">
@@ -2863,9 +2518,6 @@
           <cell r="B139" t="str">
             <v>1.083</v>
           </cell>
-          <cell r="C139">
-            <v>45</v>
-          </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
@@ -2874,9 +2526,6 @@
           <cell r="B140" t="str">
             <v>1.084</v>
           </cell>
-          <cell r="C140">
-            <v>45</v>
-          </cell>
         </row>
         <row r="141">
           <cell r="A141" t="str">
@@ -2885,9 +2534,6 @@
           <cell r="B141" t="str">
             <v>1.087</v>
           </cell>
-          <cell r="C141">
-            <v>70</v>
-          </cell>
         </row>
         <row r="142">
           <cell r="A142" t="str">
@@ -2896,9 +2542,6 @@
           <cell r="B142" t="str">
             <v>1.113</v>
           </cell>
-          <cell r="C142">
-            <v>17</v>
-          </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
@@ -2907,9 +2550,6 @@
           <cell r="B143" t="str">
             <v>1.124</v>
           </cell>
-          <cell r="C143">
-            <v>54</v>
-          </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
@@ -2918,9 +2558,6 @@
           <cell r="B144" t="str">
             <v>1.136</v>
           </cell>
-          <cell r="C144">
-            <v>101</v>
-          </cell>
         </row>
         <row r="145">
           <cell r="A145" t="str">
@@ -2929,9 +2566,6 @@
           <cell r="B145" t="str">
             <v>1.155</v>
           </cell>
-          <cell r="C145">
-            <v>46</v>
-          </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
@@ -2940,9 +2574,6 @@
           <cell r="B146" t="str">
             <v>1.156</v>
           </cell>
-          <cell r="C146">
-            <v>70</v>
-          </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
@@ -2951,9 +2582,6 @@
           <cell r="B147" t="str">
             <v>1.157</v>
           </cell>
-          <cell r="C147">
-            <v>46</v>
-          </cell>
         </row>
         <row r="148">
           <cell r="A148" t="str">
@@ -2962,9 +2590,6 @@
           <cell r="B148" t="str">
             <v>1.158</v>
           </cell>
-          <cell r="C148">
-            <v>29</v>
-          </cell>
         </row>
         <row r="149">
           <cell r="A149" t="str">
@@ -2973,9 +2598,6 @@
           <cell r="B149" t="str">
             <v>1.159</v>
           </cell>
-          <cell r="C149">
-            <v>32</v>
-          </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
@@ -2992,9 +2614,6 @@
           <cell r="B151" t="str">
             <v>1.161</v>
           </cell>
-          <cell r="C151">
-            <v>32</v>
-          </cell>
         </row>
         <row r="152">
           <cell r="A152" t="str">
@@ -3003,9 +2622,6 @@
           <cell r="B152" t="str">
             <v>1.174</v>
           </cell>
-          <cell r="C152">
-            <v>40</v>
-          </cell>
         </row>
         <row r="153">
           <cell r="A153" t="str">
@@ -3014,9 +2630,6 @@
           <cell r="B153" t="str">
             <v>1.180</v>
           </cell>
-          <cell r="C153">
-            <v>20</v>
-          </cell>
         </row>
         <row r="154">
           <cell r="A154" t="str">
@@ -3025,9 +2638,6 @@
           <cell r="B154" t="str">
             <v>1.182</v>
           </cell>
-          <cell r="C154">
-            <v>20</v>
-          </cell>
         </row>
         <row r="155">
           <cell r="A155" t="str">
@@ -3036,9 +2646,6 @@
           <cell r="B155" t="str">
             <v>1.187</v>
           </cell>
-          <cell r="C155">
-            <v>20</v>
-          </cell>
         </row>
         <row r="156">
           <cell r="A156" t="str">
@@ -3047,9 +2654,6 @@
           <cell r="B156" t="str">
             <v>1.204</v>
           </cell>
-          <cell r="C156">
-            <v>154</v>
-          </cell>
         </row>
         <row r="157">
           <cell r="A157" t="str">
@@ -3058,9 +2662,6 @@
           <cell r="B157" t="str">
             <v>1.219</v>
           </cell>
-          <cell r="C157">
-            <v>84</v>
-          </cell>
         </row>
         <row r="158">
           <cell r="A158" t="str">
@@ -3069,9 +2670,6 @@
           <cell r="B158" t="str">
             <v>1.235</v>
           </cell>
-          <cell r="C158">
-            <v>30</v>
-          </cell>
         </row>
         <row r="159">
           <cell r="A159" t="str">
@@ -3080,9 +2678,6 @@
           <cell r="B159" t="str">
             <v>1.237</v>
           </cell>
-          <cell r="C159">
-            <v>30</v>
-          </cell>
         </row>
         <row r="160">
           <cell r="A160" t="str">
@@ -3091,9 +2686,6 @@
           <cell r="B160" t="str">
             <v>1.243</v>
           </cell>
-          <cell r="C160">
-            <v>72</v>
-          </cell>
         </row>
         <row r="161">
           <cell r="A161" t="str">
@@ -3102,9 +2694,6 @@
           <cell r="B161" t="str">
             <v>1.248</v>
           </cell>
-          <cell r="C161">
-            <v>15</v>
-          </cell>
         </row>
         <row r="162">
           <cell r="A162" t="str">
@@ -3113,9 +2702,6 @@
           <cell r="B162" t="str">
             <v>1.252</v>
           </cell>
-          <cell r="C162">
-            <v>8</v>
-          </cell>
         </row>
         <row r="163">
           <cell r="A163" t="str">
@@ -3132,9 +2718,6 @@
           <cell r="B164" t="str">
             <v>10.002</v>
           </cell>
-          <cell r="C164">
-            <v>46</v>
-          </cell>
         </row>
         <row r="165">
           <cell r="A165" t="str">
@@ -3143,9 +2726,6 @@
           <cell r="B165" t="str">
             <v>10.040</v>
           </cell>
-          <cell r="C165">
-            <v>113</v>
-          </cell>
         </row>
         <row r="166">
           <cell r="A166" t="str">
@@ -3154,9 +2734,6 @@
           <cell r="B166" t="str">
             <v>10.041</v>
           </cell>
-          <cell r="C166">
-            <v>113</v>
-          </cell>
         </row>
         <row r="167">
           <cell r="A167" t="str">
@@ -3165,9 +2742,6 @@
           <cell r="B167" t="str">
             <v>10.042</v>
           </cell>
-          <cell r="C167">
-            <v>113</v>
-          </cell>
         </row>
         <row r="168">
           <cell r="A168" t="str">
@@ -3176,9 +2750,6 @@
           <cell r="B168" t="str">
             <v>10.043</v>
           </cell>
-          <cell r="C168">
-            <v>113</v>
-          </cell>
         </row>
         <row r="169">
           <cell r="A169" t="str">
@@ -3187,9 +2758,6 @@
           <cell r="B169" t="str">
             <v>10.044</v>
           </cell>
-          <cell r="C169">
-            <v>113</v>
-          </cell>
         </row>
         <row r="170">
           <cell r="A170" t="str">
@@ -3198,9 +2766,6 @@
           <cell r="B170" t="str">
             <v>10.047</v>
           </cell>
-          <cell r="C170">
-            <v>113</v>
-          </cell>
         </row>
         <row r="171">
           <cell r="A171" t="str">
@@ -3217,9 +2782,6 @@
           <cell r="B172" t="str">
             <v>10.059</v>
           </cell>
-          <cell r="C172">
-            <v>43</v>
-          </cell>
         </row>
         <row r="173">
           <cell r="A173" t="str">
@@ -3228,9 +2790,6 @@
           <cell r="B173" t="str">
             <v>10.099</v>
           </cell>
-          <cell r="C173">
-            <v>57</v>
-          </cell>
         </row>
         <row r="174">
           <cell r="A174" t="str">
@@ -3255,9 +2814,6 @@
           <cell r="B176" t="str">
             <v>11.041</v>
           </cell>
-          <cell r="C176">
-            <v>70</v>
-          </cell>
         </row>
         <row r="177">
           <cell r="A177" t="str">
@@ -3266,9 +2822,6 @@
           <cell r="B177" t="str">
             <v>11.104</v>
           </cell>
-          <cell r="C177">
-            <v>40</v>
-          </cell>
         </row>
         <row r="178">
           <cell r="A178" t="str">
@@ -3277,9 +2830,6 @@
           <cell r="B178" t="str">
             <v>11.123</v>
           </cell>
-          <cell r="C178">
-            <v>23</v>
-          </cell>
         </row>
         <row r="179">
           <cell r="A179" t="str">
@@ -3288,9 +2838,6 @@
           <cell r="B179" t="str">
             <v>11.246</v>
           </cell>
-          <cell r="C179">
-            <v>18</v>
-          </cell>
         </row>
         <row r="180">
           <cell r="A180" t="str">
@@ -3299,9 +2846,6 @@
           <cell r="B180" t="str">
             <v>12.025</v>
           </cell>
-          <cell r="C180">
-            <v>30</v>
-          </cell>
         </row>
         <row r="181">
           <cell r="A181" t="str">
@@ -3310,9 +2854,6 @@
           <cell r="B181" t="str">
             <v>12.029</v>
           </cell>
-          <cell r="C181">
-            <v>77</v>
-          </cell>
         </row>
         <row r="182">
           <cell r="A182" t="str">
@@ -3321,9 +2862,6 @@
           <cell r="B182" t="str">
             <v>12.034</v>
           </cell>
-          <cell r="C182">
-            <v>125</v>
-          </cell>
         </row>
         <row r="183">
           <cell r="A183" t="str">
@@ -3332,9 +2870,6 @@
           <cell r="B183" t="str">
             <v>12.106</v>
           </cell>
-          <cell r="C183">
-            <v>67</v>
-          </cell>
         </row>
         <row r="184">
           <cell r="A184" t="str">
@@ -3343,9 +2878,6 @@
           <cell r="B184" t="str">
             <v>12.108</v>
           </cell>
-          <cell r="C184">
-            <v>30</v>
-          </cell>
         </row>
         <row r="185">
           <cell r="A185" t="str">
@@ -3354,9 +2886,6 @@
           <cell r="B185" t="str">
             <v>12.137</v>
           </cell>
-          <cell r="C185">
-            <v>46</v>
-          </cell>
         </row>
         <row r="186">
           <cell r="A186" t="str">
@@ -3365,9 +2894,6 @@
           <cell r="B186" t="str">
             <v>12.201</v>
           </cell>
-          <cell r="C186">
-            <v>107</v>
-          </cell>
         </row>
         <row r="187">
           <cell r="A187" t="str">
@@ -3376,9 +2902,6 @@
           <cell r="B187" t="str">
             <v>13.007</v>
           </cell>
-          <cell r="C187">
-            <v>70</v>
-          </cell>
         </row>
         <row r="188">
           <cell r="A188" t="str">
@@ -3387,9 +2910,6 @@
           <cell r="B188" t="str">
             <v>13.008</v>
           </cell>
-          <cell r="C188">
-            <v>20</v>
-          </cell>
         </row>
         <row r="189">
           <cell r="A189" t="str">
@@ -3398,9 +2918,6 @@
           <cell r="B189" t="str">
             <v>13.009</v>
           </cell>
-          <cell r="C189">
-            <v>41</v>
-          </cell>
         </row>
         <row r="190">
           <cell r="A190" t="str">
@@ -3409,9 +2926,6 @@
           <cell r="B190" t="str">
             <v>13.010</v>
           </cell>
-          <cell r="C190">
-            <v>20</v>
-          </cell>
         </row>
         <row r="191">
           <cell r="A191" t="str">
@@ -3428,9 +2942,6 @@
           <cell r="B192" t="str">
             <v>13.013</v>
           </cell>
-          <cell r="C192">
-            <v>26</v>
-          </cell>
         </row>
         <row r="193">
           <cell r="A193" t="str">
@@ -3463,9 +2974,6 @@
           <cell r="B196" t="str">
             <v>13.230</v>
           </cell>
-          <cell r="C196">
-            <v>57</v>
-          </cell>
         </row>
         <row r="197">
           <cell r="A197" t="str">
@@ -3474,9 +2982,6 @@
           <cell r="B197" t="str">
             <v>14.030</v>
           </cell>
-          <cell r="C197">
-            <v>26</v>
-          </cell>
         </row>
         <row r="198">
           <cell r="A198" t="str">
@@ -3485,9 +2990,6 @@
           <cell r="B198" t="str">
             <v>14.031</v>
           </cell>
-          <cell r="C198">
-            <v>38</v>
-          </cell>
         </row>
         <row r="199">
           <cell r="A199" t="str">
@@ -3496,9 +2998,6 @@
           <cell r="B199" t="str">
             <v>15.032</v>
           </cell>
-          <cell r="C199">
-            <v>41</v>
-          </cell>
         </row>
         <row r="200">
           <cell r="A200" t="str">
@@ -3507,9 +3006,6 @@
           <cell r="B200" t="str">
             <v>15.109</v>
           </cell>
-          <cell r="C200">
-            <v>41</v>
-          </cell>
         </row>
         <row r="201">
           <cell r="A201" t="str">
@@ -3518,9 +3014,6 @@
           <cell r="B201" t="str">
             <v>15.176</v>
           </cell>
-          <cell r="C201">
-            <v>41</v>
-          </cell>
         </row>
         <row r="202">
           <cell r="A202" t="str">
@@ -3529,9 +3022,6 @@
           <cell r="B202" t="str">
             <v>15.216</v>
           </cell>
-          <cell r="C202">
-            <v>41</v>
-          </cell>
         </row>
         <row r="203">
           <cell r="A203" t="str">
@@ -3540,9 +3030,6 @@
           <cell r="B203" t="str">
             <v>15.245</v>
           </cell>
-          <cell r="C203">
-            <v>41</v>
-          </cell>
         </row>
         <row r="204">
           <cell r="A204" t="str">
@@ -3551,9 +3038,6 @@
           <cell r="B204" t="str">
             <v>16.114</v>
           </cell>
-          <cell r="C204">
-            <v>31</v>
-          </cell>
         </row>
         <row r="205">
           <cell r="A205" t="str">
@@ -3562,9 +3046,6 @@
           <cell r="B205" t="str">
             <v>16.129</v>
           </cell>
-          <cell r="C205">
-            <v>46</v>
-          </cell>
         </row>
         <row r="206">
           <cell r="A206" t="str">
@@ -3573,9 +3054,6 @@
           <cell r="B206" t="str">
             <v>16.161</v>
           </cell>
-          <cell r="C206">
-            <v>64</v>
-          </cell>
         </row>
         <row r="207">
           <cell r="A207" t="str">
@@ -3584,9 +3062,6 @@
           <cell r="B207" t="str">
             <v>16.171</v>
           </cell>
-          <cell r="C207">
-            <v>26</v>
-          </cell>
         </row>
         <row r="208">
           <cell r="A208" t="str">
@@ -3594,9 +3069,6 @@
           </cell>
           <cell r="B208" t="str">
             <v>16.250</v>
-          </cell>
-          <cell r="C208">
-            <v>78</v>
           </cell>
         </row>
         <row r="209">
@@ -3612,9 +3084,6 @@
           <cell r="B209" t="str">
             <v>17.001</v>
           </cell>
-          <cell r="C209">
-            <v>288</v>
-          </cell>
         </row>
         <row r="210">
           <cell r="A210" t="str">
@@ -3627,9 +3096,6 @@
           <cell r="B210" t="str">
             <v>17.002</v>
           </cell>
-          <cell r="C210">
-            <v>77</v>
-          </cell>
         </row>
         <row r="211">
           <cell r="A211" t="str">
@@ -3641,9 +3107,6 @@
           <cell r="B211" t="str">
             <v>17.005</v>
           </cell>
-          <cell r="C211">
-            <v>41</v>
-          </cell>
         </row>
         <row r="212">
           <cell r="A212" t="str">
@@ -3652,9 +3115,6 @@
           </cell>
           <cell r="B212" t="str">
             <v>17.040</v>
-          </cell>
-          <cell r="C212">
-            <v>190</v>
           </cell>
         </row>
         <row r="213">
@@ -3681,9 +3141,6 @@
           <cell r="B214" t="str">
             <v>17.044</v>
           </cell>
-          <cell r="C214">
-            <v>163</v>
-          </cell>
         </row>
         <row r="215">
           <cell r="A215" t="str">
@@ -3697,9 +3154,6 @@
           </cell>
           <cell r="B215" t="str">
             <v>17.045</v>
-          </cell>
-          <cell r="C215">
-            <v>49</v>
           </cell>
         </row>
         <row r="216">
@@ -3716,9 +3170,6 @@
           <cell r="B216" t="str">
             <v>17.046</v>
           </cell>
-          <cell r="C216">
-            <v>590</v>
-          </cell>
         </row>
         <row r="217">
           <cell r="A217" t="str">
@@ -3726,9 +3177,6 @@
           </cell>
           <cell r="B217" t="str">
             <v>17.050</v>
-          </cell>
-          <cell r="C217">
-            <v>47</v>
           </cell>
         </row>
         <row r="218">
@@ -3762,9 +3210,6 @@
           <cell r="B220" t="str">
             <v>18.223</v>
           </cell>
-          <cell r="C220">
-            <v>32</v>
-          </cell>
         </row>
         <row r="221">
           <cell r="A221" t="str">
@@ -3773,9 +3218,6 @@
           <cell r="B221" t="str">
             <v>18.224</v>
           </cell>
-          <cell r="C221">
-            <v>23</v>
-          </cell>
         </row>
         <row r="222">
           <cell r="A222" t="str">
@@ -3792,9 +3234,6 @@
           <cell r="B223" t="str">
             <v>19.015</v>
           </cell>
-          <cell r="C223">
-            <v>26</v>
-          </cell>
         </row>
         <row r="224">
           <cell r="A224" t="str">
@@ -3803,9 +3242,6 @@
           <cell r="B224" t="str">
             <v>2.001</v>
           </cell>
-          <cell r="C224">
-            <v>15</v>
-          </cell>
         </row>
         <row r="225">
           <cell r="A225" t="str">
@@ -3814,9 +3250,6 @@
           <cell r="B225" t="str">
             <v>2.003</v>
           </cell>
-          <cell r="C225">
-            <v>30</v>
-          </cell>
         </row>
         <row r="226">
           <cell r="A226" t="str">
@@ -3825,9 +3258,6 @@
           <cell r="B226" t="str">
             <v>2.004</v>
           </cell>
-          <cell r="C226">
-            <v>15</v>
-          </cell>
         </row>
         <row r="227">
           <cell r="A227" t="str">
@@ -3836,9 +3266,6 @@
           <cell r="B227" t="str">
             <v>2.006</v>
           </cell>
-          <cell r="C227">
-            <v>26</v>
-          </cell>
         </row>
         <row r="228">
           <cell r="A228" t="str">
@@ -3847,9 +3274,6 @@
           <cell r="B228" t="str">
             <v>2.008</v>
           </cell>
-          <cell r="C228">
-            <v>57</v>
-          </cell>
         </row>
         <row r="229">
           <cell r="A229" t="str">
@@ -3857,9 +3281,6 @@
           </cell>
           <cell r="B229" t="str">
             <v>2.009</v>
-          </cell>
-          <cell r="C229">
-            <v>26</v>
           </cell>
         </row>
         <row r="230">
@@ -3869,9 +3290,6 @@
           </cell>
           <cell r="B230" t="str">
             <v>2.011</v>
-          </cell>
-          <cell r="C230">
-            <v>13</v>
           </cell>
         </row>
         <row r="231">
@@ -3893,9 +3311,6 @@
           <cell r="B232" t="str">
             <v>2.029</v>
           </cell>
-          <cell r="C232">
-            <v>26</v>
-          </cell>
         </row>
         <row r="233">
           <cell r="A233" t="str">
@@ -3904,9 +3319,6 @@
           <cell r="B233" t="str">
             <v>2.058</v>
           </cell>
-          <cell r="C233">
-            <v>15</v>
-          </cell>
         </row>
         <row r="234">
           <cell r="A234" t="str">
@@ -3915,9 +3327,6 @@
           <cell r="B234" t="str">
             <v>2.091</v>
           </cell>
-          <cell r="C234">
-            <v>31</v>
-          </cell>
         </row>
         <row r="235">
           <cell r="A235" t="str">
@@ -3926,9 +3335,6 @@
           <cell r="B235" t="str">
             <v>2.092</v>
           </cell>
-          <cell r="C235">
-            <v>43</v>
-          </cell>
         </row>
         <row r="236">
           <cell r="A236" t="str">
@@ -3937,9 +3343,6 @@
           <cell r="B236" t="str">
             <v>2.093</v>
           </cell>
-          <cell r="C236">
-            <v>189</v>
-          </cell>
         </row>
         <row r="237">
           <cell r="A237" t="str">
@@ -3948,9 +3351,6 @@
           <cell r="B237" t="str">
             <v>2.094</v>
           </cell>
-          <cell r="C237">
-            <v>16</v>
-          </cell>
         </row>
         <row r="238">
           <cell r="A238" t="str">
@@ -3959,9 +3359,6 @@
           <cell r="B238" t="str">
             <v>2.095</v>
           </cell>
-          <cell r="C238">
-            <v>30</v>
-          </cell>
         </row>
         <row r="239">
           <cell r="A239" t="str">
@@ -3970,9 +3367,6 @@
           <cell r="B239" t="str">
             <v>2.130</v>
           </cell>
-          <cell r="C239">
-            <v>16</v>
-          </cell>
         </row>
         <row r="240">
           <cell r="A240" t="str">
@@ -3981,9 +3375,6 @@
           <cell r="B240" t="str">
             <v>2.131</v>
           </cell>
-          <cell r="C240">
-            <v>39</v>
-          </cell>
         </row>
         <row r="241">
           <cell r="A241" t="str">
@@ -3992,9 +3383,6 @@
           <cell r="B241" t="str">
             <v>2.132</v>
           </cell>
-          <cell r="C241" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="242">
           <cell r="A242" t="str">
@@ -4003,9 +3391,6 @@
           <cell r="B242" t="str">
             <v>2.133</v>
           </cell>
-          <cell r="C242">
-            <v>16</v>
-          </cell>
         </row>
         <row r="243">
           <cell r="A243" t="str">
@@ -4022,9 +3407,6 @@
           <cell r="B244" t="str">
             <v>2.143</v>
           </cell>
-          <cell r="C244">
-            <v>72</v>
-          </cell>
         </row>
         <row r="245">
           <cell r="A245" t="str">
@@ -4033,9 +3415,6 @@
           <cell r="B245" t="str">
             <v>2.144</v>
           </cell>
-          <cell r="C245">
-            <v>43</v>
-          </cell>
         </row>
         <row r="246">
           <cell r="A246" t="str">
@@ -4044,9 +3423,6 @@
           <cell r="B246" t="str">
             <v>2.145</v>
           </cell>
-          <cell r="C246">
-            <v>43</v>
-          </cell>
         </row>
         <row r="247">
           <cell r="A247" t="str">
@@ -4054,9 +3430,6 @@
           </cell>
           <cell r="B247" t="str">
             <v>2.148</v>
-          </cell>
-          <cell r="C247">
-            <v>29</v>
           </cell>
         </row>
         <row r="248">
@@ -4082,9 +3455,6 @@
           <cell r="B248" t="str">
             <v>2.154</v>
           </cell>
-          <cell r="C248">
-            <v>55</v>
-          </cell>
         </row>
         <row r="249">
           <cell r="A249" t="str">
@@ -4093,9 +3463,6 @@
           <cell r="B249" t="str">
             <v>2.162</v>
           </cell>
-          <cell r="C249">
-            <v>46</v>
-          </cell>
         </row>
         <row r="250">
           <cell r="A250" t="str">
@@ -4104,9 +3471,6 @@
           <cell r="B250" t="str">
             <v>2.163</v>
           </cell>
-          <cell r="C250">
-            <v>46</v>
-          </cell>
         </row>
         <row r="251">
           <cell r="A251" t="str">
@@ -4115,9 +3479,6 @@
           <cell r="B251" t="str">
             <v>2.164</v>
           </cell>
-          <cell r="C251">
-            <v>40</v>
-          </cell>
         </row>
         <row r="252">
           <cell r="A252" t="str">
@@ -4126,9 +3487,6 @@
           <cell r="B252" t="str">
             <v>2.172</v>
           </cell>
-          <cell r="C252">
-            <v>16</v>
-          </cell>
         </row>
         <row r="253">
           <cell r="A253" t="str">
@@ -4137,9 +3495,6 @@
           <cell r="B253" t="str">
             <v>2.177</v>
           </cell>
-          <cell r="C253">
-            <v>30</v>
-          </cell>
         </row>
         <row r="254">
           <cell r="A254" t="str">
@@ -4148,9 +3503,6 @@
           <cell r="B254" t="str">
             <v>2.178</v>
           </cell>
-          <cell r="C254">
-            <v>35</v>
-          </cell>
         </row>
         <row r="255">
           <cell r="A255" t="str">
@@ -4159,9 +3511,6 @@
           <cell r="B255" t="str">
             <v>2.182</v>
           </cell>
-          <cell r="C255">
-            <v>46</v>
-          </cell>
         </row>
         <row r="256">
           <cell r="A256" t="str">
@@ -4170,9 +3519,6 @@
           <cell r="B256" t="str">
             <v>2.194</v>
           </cell>
-          <cell r="C256">
-            <v>46</v>
-          </cell>
         </row>
         <row r="257">
           <cell r="A257" t="str">
@@ -4181,9 +3527,6 @@
           <cell r="B257" t="str">
             <v>2.207</v>
           </cell>
-          <cell r="C257">
-            <v>41</v>
-          </cell>
         </row>
         <row r="258">
           <cell r="A258" t="str">
@@ -4192,9 +3535,6 @@
           <cell r="B258" t="str">
             <v>2.208</v>
           </cell>
-          <cell r="C258">
-            <v>41</v>
-          </cell>
         </row>
         <row r="259">
           <cell r="A259" t="str">
@@ -4211,9 +3551,6 @@
           <cell r="B260" t="str">
             <v>2.212</v>
           </cell>
-          <cell r="C260">
-            <v>46</v>
-          </cell>
         </row>
         <row r="261">
           <cell r="A261" t="str">
@@ -4222,9 +3559,6 @@
           <cell r="B261" t="str">
             <v>2.213</v>
           </cell>
-          <cell r="C261">
-            <v>46</v>
-          </cell>
         </row>
         <row r="262">
           <cell r="A262" t="str">
@@ -4233,9 +3567,6 @@
           <cell r="B262" t="str">
             <v>2.226</v>
           </cell>
-          <cell r="C262">
-            <v>8</v>
-          </cell>
         </row>
         <row r="263">
           <cell r="A263" t="str">
@@ -4244,9 +3575,6 @@
           <cell r="B263" t="str">
             <v>2.228</v>
           </cell>
-          <cell r="C263">
-            <v>32</v>
-          </cell>
         </row>
         <row r="264">
           <cell r="A264" t="str">
@@ -4255,9 +3583,6 @@
           <cell r="B264" t="str">
             <v>2.256</v>
           </cell>
-          <cell r="C264">
-            <v>3</v>
-          </cell>
         </row>
         <row r="265">
           <cell r="A265" t="str">
@@ -4266,9 +3591,6 @@
           <cell r="B265" t="str">
             <v>2.257</v>
           </cell>
-          <cell r="C265">
-            <v>3</v>
-          </cell>
         </row>
         <row r="266">
           <cell r="A266" t="str">
@@ -4277,9 +3599,6 @@
           <cell r="B266" t="str">
             <v>2.258</v>
           </cell>
-          <cell r="C266">
-            <v>3</v>
-          </cell>
         </row>
         <row r="267">
           <cell r="A267" t="str">
@@ -4287,9 +3606,6 @@
           </cell>
           <cell r="B267" t="str">
             <v>2.261</v>
-          </cell>
-          <cell r="C267">
-            <v>3</v>
           </cell>
         </row>
         <row r="268">
@@ -4312,9 +3628,6 @@
           <cell r="B268" t="str">
             <v>20.001</v>
           </cell>
-          <cell r="C268">
-            <v>227</v>
-          </cell>
         </row>
         <row r="269">
           <cell r="A269" t="str">
@@ -4322,9 +3635,6 @@
           </cell>
           <cell r="B269" t="str">
             <v>20.002</v>
-          </cell>
-          <cell r="C269">
-            <v>130</v>
           </cell>
         </row>
         <row r="270">
@@ -4351,9 +3661,6 @@
           <cell r="B270" t="str">
             <v>20.004</v>
           </cell>
-          <cell r="C270" t="str">
-            <v>ESCALADO</v>
-          </cell>
         </row>
         <row r="271">
           <cell r="A271" t="str">
@@ -4370,9 +3677,6 @@
           <cell r="B271" t="str">
             <v>20.010</v>
           </cell>
-          <cell r="C271">
-            <v>100</v>
-          </cell>
         </row>
         <row r="272">
           <cell r="A272" t="str">
@@ -4384,9 +3688,6 @@
           <cell r="B272" t="str">
             <v>20.011</v>
           </cell>
-          <cell r="C272">
-            <v>84</v>
-          </cell>
         </row>
         <row r="273">
           <cell r="A273" t="str">
@@ -4395,9 +3696,6 @@
           <cell r="B273" t="str">
             <v>3.004</v>
           </cell>
-          <cell r="C273">
-            <v>40</v>
-          </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
@@ -4406,9 +3704,6 @@
           <cell r="B274" t="str">
             <v>3.005</v>
           </cell>
-          <cell r="C274">
-            <v>77</v>
-          </cell>
         </row>
         <row r="275">
           <cell r="A275" t="str">
@@ -4416,9 +3711,6 @@
           </cell>
           <cell r="B275" t="str">
             <v>3.006</v>
-          </cell>
-          <cell r="C275">
-            <v>77</v>
           </cell>
         </row>
         <row r="276">
@@ -4449,9 +3741,6 @@
           <cell r="B276" t="str">
             <v>3.007</v>
           </cell>
-          <cell r="C276">
-            <v>582</v>
-          </cell>
         </row>
         <row r="277">
           <cell r="A277" t="str">
@@ -4459,9 +3748,6 @@
           </cell>
           <cell r="B277" t="str">
             <v>3.008</v>
-          </cell>
-          <cell r="C277">
-            <v>42</v>
           </cell>
         </row>
         <row r="278">
@@ -4472,9 +3758,6 @@
           <cell r="B278" t="str">
             <v>3.010</v>
           </cell>
-          <cell r="C278">
-            <v>13</v>
-          </cell>
         </row>
         <row r="279">
           <cell r="A279" t="str">
@@ -4483,9 +3766,6 @@
           <cell r="B279" t="str">
             <v>3.011</v>
           </cell>
-          <cell r="C279">
-            <v>28</v>
-          </cell>
         </row>
         <row r="280">
           <cell r="A280" t="str">
@@ -4494,9 +3774,6 @@
           <cell r="B280" t="str">
             <v>3.012</v>
           </cell>
-          <cell r="C280">
-            <v>41</v>
-          </cell>
         </row>
         <row r="281">
           <cell r="A281" t="str">
@@ -4505,9 +3782,6 @@
           <cell r="B281" t="str">
             <v>3.013</v>
           </cell>
-          <cell r="C281">
-            <v>33</v>
-          </cell>
         </row>
         <row r="282">
           <cell r="A282" t="str">
@@ -4516,9 +3790,6 @@
           <cell r="B282" t="str">
             <v>3.014</v>
           </cell>
-          <cell r="C282">
-            <v>42</v>
-          </cell>
         </row>
         <row r="283">
           <cell r="A283" t="str">
@@ -4535,9 +3806,6 @@
           <cell r="B284" t="str">
             <v>3.020</v>
           </cell>
-          <cell r="C284">
-            <v>40</v>
-          </cell>
         </row>
         <row r="285">
           <cell r="A285" t="str">
@@ -4546,9 +3814,6 @@
           <cell r="B285" t="str">
             <v>3.021</v>
           </cell>
-          <cell r="C285">
-            <v>40</v>
-          </cell>
         </row>
         <row r="286">
           <cell r="A286" t="str">
@@ -4557,9 +3822,6 @@
           <cell r="B286" t="str">
             <v>3.022</v>
           </cell>
-          <cell r="C286">
-            <v>217</v>
-          </cell>
         </row>
         <row r="287">
           <cell r="A287" t="str">
@@ -4568,9 +3830,6 @@
           <cell r="B287" t="str">
             <v>3.023</v>
           </cell>
-          <cell r="C287">
-            <v>40</v>
-          </cell>
         </row>
         <row r="288">
           <cell r="A288" t="str">
@@ -4579,9 +3838,6 @@
           <cell r="B288" t="str">
             <v>3.025</v>
           </cell>
-          <cell r="C288">
-            <v>30</v>
-          </cell>
         </row>
         <row r="289">
           <cell r="A289" t="str">
@@ -4590,9 +3846,6 @@
           <cell r="B289" t="str">
             <v>3.026</v>
           </cell>
-          <cell r="C289">
-            <v>40</v>
-          </cell>
         </row>
         <row r="290">
           <cell r="A290" t="str">
@@ -4601,9 +3854,6 @@
           <cell r="B290" t="str">
             <v>3.028</v>
           </cell>
-          <cell r="C290">
-            <v>30</v>
-          </cell>
         </row>
         <row r="291">
           <cell r="A291" t="str">
@@ -4612,9 +3862,6 @@
           <cell r="B291" t="str">
             <v>3.029</v>
           </cell>
-          <cell r="C291">
-            <v>30</v>
-          </cell>
         </row>
         <row r="292">
           <cell r="A292" t="str">
@@ -4631,9 +3878,6 @@
           <cell r="B293" t="str">
             <v>3.051</v>
           </cell>
-          <cell r="C293">
-            <v>40</v>
-          </cell>
         </row>
         <row r="294">
           <cell r="A294" t="str">
@@ -4642,9 +3886,6 @@
           <cell r="B294" t="str">
             <v>3.060</v>
           </cell>
-          <cell r="C294">
-            <v>78</v>
-          </cell>
         </row>
         <row r="295">
           <cell r="A295" t="str">
@@ -4653,9 +3894,6 @@
           <cell r="B295" t="str">
             <v>3.067</v>
           </cell>
-          <cell r="C295">
-            <v>40</v>
-          </cell>
         </row>
         <row r="296">
           <cell r="A296" t="str">
@@ -4672,9 +3910,6 @@
           <cell r="B297" t="str">
             <v>3.076</v>
           </cell>
-          <cell r="C297">
-            <v>40</v>
-          </cell>
         </row>
         <row r="298">
           <cell r="A298" t="str">
@@ -4683,9 +3918,6 @@
           <cell r="B298" t="str">
             <v>3.096</v>
           </cell>
-          <cell r="C298">
-            <v>30</v>
-          </cell>
         </row>
         <row r="299">
           <cell r="A299" t="str">
@@ -4694,9 +3926,6 @@
           <cell r="B299" t="str">
             <v>3.098</v>
           </cell>
-          <cell r="C299">
-            <v>55</v>
-          </cell>
         </row>
         <row r="300">
           <cell r="A300" t="str">
@@ -4705,9 +3934,6 @@
           <cell r="B300" t="str">
             <v>3.101</v>
           </cell>
-          <cell r="C300">
-            <v>39</v>
-          </cell>
         </row>
         <row r="301">
           <cell r="A301" t="str">
@@ -4715,9 +3941,6 @@
           </cell>
           <cell r="B301" t="str">
             <v>3.149</v>
-          </cell>
-          <cell r="C301">
-            <v>66</v>
           </cell>
         </row>
         <row r="302">
@@ -4728,9 +3951,6 @@
           <cell r="B302" t="str">
             <v>3.150</v>
           </cell>
-          <cell r="C302">
-            <v>79</v>
-          </cell>
         </row>
         <row r="303">
           <cell r="A303" t="str">
@@ -4739,9 +3959,6 @@
           <cell r="B303" t="str">
             <v>3.183</v>
           </cell>
-          <cell r="C303">
-            <v>65</v>
-          </cell>
         </row>
         <row r="304">
           <cell r="A304" t="str">
@@ -4750,9 +3967,6 @@
           <cell r="B304" t="str">
             <v>3.184</v>
           </cell>
-          <cell r="C304">
-            <v>57</v>
-          </cell>
         </row>
         <row r="305">
           <cell r="A305" t="str">
@@ -4761,9 +3975,6 @@
           <cell r="B305" t="str">
             <v>3.185</v>
           </cell>
-          <cell r="C305">
-            <v>40</v>
-          </cell>
         </row>
         <row r="306">
           <cell r="A306" t="str">
@@ -4772,9 +3983,6 @@
           <cell r="B306" t="str">
             <v>3.186</v>
           </cell>
-          <cell r="C306">
-            <v>40</v>
-          </cell>
         </row>
         <row r="307">
           <cell r="A307" t="str">
@@ -4783,9 +3991,6 @@
           <cell r="B307" t="str">
             <v>3.187</v>
           </cell>
-          <cell r="C307">
-            <v>57</v>
-          </cell>
         </row>
         <row r="308">
           <cell r="A308" t="str">
@@ -4794,9 +3999,6 @@
           <cell r="B308" t="str">
             <v>3.188</v>
           </cell>
-          <cell r="C308">
-            <v>40</v>
-          </cell>
         </row>
         <row r="309">
           <cell r="A309" t="str">
@@ -4805,9 +4007,6 @@
           <cell r="B309" t="str">
             <v>3.189</v>
           </cell>
-          <cell r="C309">
-            <v>40</v>
-          </cell>
         </row>
         <row r="310">
           <cell r="A310" t="str">
@@ -4816,9 +4015,6 @@
           <cell r="B310" t="str">
             <v>3.214</v>
           </cell>
-          <cell r="C310">
-            <v>40</v>
-          </cell>
         </row>
         <row r="311">
           <cell r="A311" t="str">
@@ -4827,9 +4023,6 @@
           <cell r="B311" t="str">
             <v>3.218</v>
           </cell>
-          <cell r="C311">
-            <v>40</v>
-          </cell>
         </row>
         <row r="312">
           <cell r="A312" t="str">
@@ -4838,9 +4031,6 @@
           <cell r="B312" t="str">
             <v>3.248</v>
           </cell>
-          <cell r="C312">
-            <v>41</v>
-          </cell>
         </row>
         <row r="313">
           <cell r="A313" t="str">
@@ -4849,9 +4039,6 @@
           <cell r="B313" t="str">
             <v>4.137</v>
           </cell>
-          <cell r="C313">
-            <v>40</v>
-          </cell>
         </row>
         <row r="314">
           <cell r="A314" t="str">
@@ -4860,9 +4047,6 @@
           <cell r="B314" t="str">
             <v>4.193</v>
           </cell>
-          <cell r="C314">
-            <v>67</v>
-          </cell>
         </row>
         <row r="315">
           <cell r="A315" t="str">
@@ -4870,9 +4054,6 @@
           </cell>
           <cell r="B315" t="str">
             <v>4.225</v>
-          </cell>
-          <cell r="C315">
-            <v>50</v>
           </cell>
         </row>
         <row r="316">
@@ -4883,9 +4064,6 @@
           <cell r="B316" t="str">
             <v>4.240</v>
           </cell>
-          <cell r="C316">
-            <v>140</v>
-          </cell>
         </row>
         <row r="317">
           <cell r="A317" t="str">
@@ -4894,9 +4072,6 @@
           <cell r="B317" t="str">
             <v>5.005</v>
           </cell>
-          <cell r="C317">
-            <v>78</v>
-          </cell>
         </row>
         <row r="318">
           <cell r="A318" t="str">
@@ -4905,9 +4080,6 @@
           <cell r="B318" t="str">
             <v>5.038</v>
           </cell>
-          <cell r="C318">
-            <v>43</v>
-          </cell>
         </row>
         <row r="319">
           <cell r="A319" t="str">
@@ -4915,9 +4087,6 @@
           </cell>
           <cell r="B319" t="str">
             <v>5.047</v>
-          </cell>
-          <cell r="C319">
-            <v>28</v>
           </cell>
         </row>
         <row r="320">
@@ -4932,9 +4101,6 @@
           <cell r="B320" t="str">
             <v>6.008</v>
           </cell>
-          <cell r="C320">
-            <v>108</v>
-          </cell>
         </row>
         <row r="321">
           <cell r="A321" t="str">
@@ -4948,9 +4114,6 @@
           <cell r="B321" t="str">
             <v>6.009</v>
           </cell>
-          <cell r="C321">
-            <v>91</v>
-          </cell>
         </row>
         <row r="322">
           <cell r="A322" t="str">
@@ -4959,9 +4122,6 @@
           <cell r="B322" t="str">
             <v>6.170</v>
           </cell>
-          <cell r="C322">
-            <v>57</v>
-          </cell>
         </row>
         <row r="323">
           <cell r="A323" t="str">
@@ -4970,9 +4130,6 @@
           <cell r="B323" t="str">
             <v>6.242</v>
           </cell>
-          <cell r="C323">
-            <v>71</v>
-          </cell>
         </row>
         <row r="324">
           <cell r="A324" t="str">
@@ -4981,9 +4138,6 @@
           <cell r="B324" t="str">
             <v>7.010</v>
           </cell>
-          <cell r="C324">
-            <v>41</v>
-          </cell>
         </row>
         <row r="325">
           <cell r="A325" t="str">
@@ -4992,9 +4146,6 @@
           <cell r="B325" t="str">
             <v>7.011</v>
           </cell>
-          <cell r="C325">
-            <v>36</v>
-          </cell>
         </row>
         <row r="326">
           <cell r="A326" t="str">
@@ -5003,9 +4154,6 @@
           <cell r="B326" t="str">
             <v>7.179</v>
           </cell>
-          <cell r="C326">
-            <v>24</v>
-          </cell>
         </row>
         <row r="327">
           <cell r="A327" t="str">
@@ -5014,9 +4162,6 @@
           <cell r="B327" t="str">
             <v>8.024</v>
           </cell>
-          <cell r="C327">
-            <v>72</v>
-          </cell>
         </row>
         <row r="328">
           <cell r="A328" t="str">
@@ -5025,9 +4170,6 @@
           <cell r="B328" t="str">
             <v>8.025</v>
           </cell>
-          <cell r="C328">
-            <v>46</v>
-          </cell>
         </row>
         <row r="329">
           <cell r="A329" t="str">
@@ -5036,9 +4178,6 @@
           <cell r="B329" t="str">
             <v>8.026</v>
           </cell>
-          <cell r="C329">
-            <v>101</v>
-          </cell>
         </row>
         <row r="330">
           <cell r="A330" t="str">
@@ -5047,9 +4186,6 @@
           <cell r="B330" t="str">
             <v>8.027</v>
           </cell>
-          <cell r="C330">
-            <v>101</v>
-          </cell>
         </row>
         <row r="331">
           <cell r="A331" t="str">
@@ -5058,9 +4194,6 @@
           <cell r="B331" t="str">
             <v>8.132</v>
           </cell>
-          <cell r="C331">
-            <v>36</v>
-          </cell>
         </row>
         <row r="332">
           <cell r="A332" t="str">
@@ -5069,9 +4202,6 @@
           <cell r="B332" t="str">
             <v>8.133</v>
           </cell>
-          <cell r="C332">
-            <v>57</v>
-          </cell>
         </row>
         <row r="333">
           <cell r="A333" t="str">
@@ -5080,9 +4210,6 @@
           <cell r="B333" t="str">
             <v>8.136</v>
           </cell>
-          <cell r="C333">
-            <v>57</v>
-          </cell>
         </row>
         <row r="334">
           <cell r="A334" t="str">
@@ -5091,9 +4218,6 @@
           <cell r="B334" t="str">
             <v>8.141</v>
           </cell>
-          <cell r="C334">
-            <v>94</v>
-          </cell>
         </row>
         <row r="335">
           <cell r="A335" t="str">
@@ -5102,9 +4226,6 @@
           <cell r="B335" t="str">
             <v>8.150</v>
           </cell>
-          <cell r="C335">
-            <v>67</v>
-          </cell>
         </row>
         <row r="336">
           <cell r="A336" t="str">
@@ -5113,9 +4234,6 @@
           <cell r="B336" t="str">
             <v>8.151</v>
           </cell>
-          <cell r="C336">
-            <v>68</v>
-          </cell>
         </row>
         <row r="337">
           <cell r="A337" t="str">
@@ -5124,9 +4242,6 @@
           <cell r="B337" t="str">
             <v>8.167</v>
           </cell>
-          <cell r="C337">
-            <v>56</v>
-          </cell>
         </row>
         <row r="338">
           <cell r="A338" t="str">
@@ -5135,9 +4250,6 @@
           <cell r="B338" t="str">
             <v>9.039</v>
           </cell>
-          <cell r="C338">
-            <v>123</v>
-          </cell>
         </row>
         <row r="339">
           <cell r="A339" t="str">
@@ -5146,9 +4258,6 @@
           <cell r="B339" t="str">
             <v>9.060</v>
           </cell>
-          <cell r="C339">
-            <v>41</v>
-          </cell>
         </row>
         <row r="340">
           <cell r="A340" t="str">
@@ -5157,9 +4266,6 @@
           <cell r="B340" t="str">
             <v>9.206</v>
           </cell>
-          <cell r="C340">
-            <v>64</v>
-          </cell>
         </row>
         <row r="341">
           <cell r="A341" t="str">
@@ -5167,9 +4273,6 @@
           </cell>
           <cell r="B341" t="str">
             <v>9.300</v>
-          </cell>
-          <cell r="C341">
-            <v>77</v>
           </cell>
         </row>
       </sheetData>
@@ -5201,18 +4304,16 @@
     <tableColumn id="13" xr3:uid="{415AF5E4-99D4-40A7-951B-16FD91BE47AD}" name="CONCEPTO FACT" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(VLOOKUP(K7, [1]Conceptos!A:B, 2, FALSE), "")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{92F996E1-80A3-43D7-AFC0-014D474D35EC}" name="IMPORTE" dataDxfId="0" dataCellStyle="Moneda">
-      <calculatedColumnFormula>IFERROR(VLOOKUP(L7, [1]Conceptos!B:C, 2, FALSE), "")</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="14" xr3:uid="{92F996E1-80A3-43D7-AFC0-014D474D35EC}" name="IMPORTE" dataDxfId="0" dataCellStyle="Moneda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5250,7 +4351,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5356,7 +4457,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5498,7 +4599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5507,24 +4608,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81E19E29-33CB-4752-99FD-DF0937A63807}">
   <dimension ref="A6:M62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="16" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="2.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="67.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" style="16" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="2.453125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="67.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.85546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" style="17" customWidth="1"/>
     <col min="13" max="13" width="14" style="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>108</v>
       </c>
@@ -5565,7 +4666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>2418</v>
       </c>
@@ -5601,12 +4702,9 @@
         <f>IFERROR(VLOOKUP(K7, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M7" s="7">
-        <f>IFERROR(VLOOKUP(L7, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8">
         <v>1650</v>
       </c>
@@ -5642,12 +4740,9 @@
         <f>IFERROR(VLOOKUP(K8, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.058</v>
       </c>
-      <c r="M8" s="11">
-        <f>IFERROR(VLOOKUP(L8, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>15</v>
-      </c>
+      <c r="M8" s="11"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>1650</v>
       </c>
@@ -5684,11 +4779,10 @@
         <v>0.250</v>
       </c>
       <c r="M9" s="7">
-        <f>IFERROR(VLOOKUP(L9, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>2523</v>
       </c>
@@ -5725,11 +4819,10 @@
         <v>0.027</v>
       </c>
       <c r="M10" s="7">
-        <f>IFERROR(VLOOKUP(L10, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>2523</v>
       </c>
@@ -5766,11 +4859,10 @@
         <v>0.027</v>
       </c>
       <c r="M11" s="7">
-        <f>IFERROR(VLOOKUP(L11, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>1306</v>
       </c>
@@ -5806,12 +4898,9 @@
         <f>IFERROR(VLOOKUP(K12, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.228</v>
       </c>
-      <c r="M12" s="7">
-        <f>IFERROR(VLOOKUP(L12, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>32</v>
-      </c>
+      <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>1815</v>
       </c>
@@ -5845,11 +4934,9 @@
         <f>IFERROR(VLOOKUP(K13, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M13" s="7">
-        <v>30</v>
-      </c>
+      <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>1815</v>
       </c>
@@ -5883,11 +4970,9 @@
         <f>IFERROR(VLOOKUP(K14, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.133</v>
       </c>
-      <c r="M14" s="7">
-        <v>31</v>
-      </c>
+      <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>2545</v>
       </c>
@@ -5923,12 +5008,9 @@
         <f>IFERROR(VLOOKUP(K15, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>1.156</v>
       </c>
-      <c r="M15" s="7">
-        <f>IFERROR(VLOOKUP(L15, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>70</v>
-      </c>
+      <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>2418</v>
       </c>
@@ -5964,12 +5046,9 @@
         <f>IFERROR(VLOOKUP(K16, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>1.156</v>
       </c>
-      <c r="M16" s="7">
-        <f>IFERROR(VLOOKUP(L16, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>70</v>
-      </c>
+      <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <v>1650</v>
       </c>
@@ -6005,12 +5084,9 @@
         <f>IFERROR(VLOOKUP(K17, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.027</v>
       </c>
-      <c r="M17" s="7">
-        <f>IFERROR(VLOOKUP(L17, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>26</v>
-      </c>
+      <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4">
         <v>61</v>
       </c>
@@ -6044,11 +5120,9 @@
         <f>IFERROR(VLOOKUP(K18, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M18" s="7">
-        <v>30</v>
-      </c>
+      <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>1279</v>
       </c>
@@ -6082,11 +5156,9 @@
         <f>IFERROR(VLOOKUP(K19, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M19" s="7">
-        <v>30</v>
-      </c>
+      <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4">
         <v>1306</v>
       </c>
@@ -6120,12 +5192,9 @@
         <f>IFERROR(VLOOKUP(K20, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M20" s="7">
-        <f>IFERROR(VLOOKUP(L20, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>15</v>
-      </c>
+      <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4">
         <v>1436</v>
       </c>
@@ -6159,12 +5228,9 @@
         <f>IFERROR(VLOOKUP(K21, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M21" s="7">
-        <f>IFERROR(VLOOKUP(L21, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>15</v>
-      </c>
+      <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <v>1436</v>
       </c>
@@ -6198,12 +5264,9 @@
         <f>IFERROR(VLOOKUP(K22, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.094</v>
       </c>
-      <c r="M22" s="7">
-        <f>IFERROR(VLOOKUP(L22, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>16</v>
-      </c>
+      <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4">
         <v>2274</v>
       </c>
@@ -6237,12 +5300,9 @@
         <f>IFERROR(VLOOKUP(K23, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>2.001</v>
       </c>
-      <c r="M23" s="7">
-        <f>IFERROR(VLOOKUP(L23, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>15</v>
-      </c>
+      <c r="M23" s="7"/>
     </row>
-    <row r="24" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4">
         <v>1599</v>
       </c>
@@ -6278,12 +5338,9 @@
         <f>IFERROR(VLOOKUP(K24, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M24" s="7">
-        <f>IFERROR(VLOOKUP(L24, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M24" s="7"/>
     </row>
-    <row r="25" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4">
         <v>1436</v>
       </c>
@@ -6319,12 +5376,9 @@
         <f>IFERROR(VLOOKUP(K25, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M25" s="7">
-        <f>IFERROR(VLOOKUP(L25, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M25" s="7"/>
     </row>
-    <row r="26" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4">
         <v>2383</v>
       </c>
@@ -6361,11 +5415,10 @@
         <v>0.250</v>
       </c>
       <c r="M26" s="7">
-        <f>IFERROR(VLOOKUP(L26, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="4">
         <v>1815</v>
       </c>
@@ -6401,12 +5454,9 @@
         <f>IFERROR(VLOOKUP(K27, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M27" s="7">
-        <f>IFERROR(VLOOKUP(L27, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M27" s="7"/>
     </row>
-    <row r="28" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="4">
         <v>1436</v>
       </c>
@@ -6442,12 +5492,9 @@
         <f>IFERROR(VLOOKUP(K28, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.022</v>
       </c>
-      <c r="M28" s="7">
-        <f>IFERROR(VLOOKUP(L28, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>9</v>
-      </c>
+      <c r="M28" s="7"/>
     </row>
-    <row r="29" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="4">
         <v>1240</v>
       </c>
@@ -6483,12 +5530,9 @@
         <f>IFERROR(VLOOKUP(K29, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M29" s="7">
-        <f>IFERROR(VLOOKUP(L29, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M29" s="7"/>
     </row>
-    <row r="30" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="4">
         <v>1591</v>
       </c>
@@ -6524,12 +5568,9 @@
         <f>IFERROR(VLOOKUP(K30, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>1.156</v>
       </c>
-      <c r="M30" s="7">
-        <f>IFERROR(VLOOKUP(L30, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>70</v>
-      </c>
+      <c r="M30" s="7"/>
     </row>
-    <row r="31" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="4">
         <v>2574</v>
       </c>
@@ -6565,12 +5606,9 @@
         <f>IFERROR(VLOOKUP(K31, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>1.182</v>
       </c>
-      <c r="M31" s="7">
-        <f>IFERROR(VLOOKUP(L31, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>20</v>
-      </c>
+      <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4">
         <v>2418</v>
       </c>
@@ -6606,12 +5644,9 @@
         <f>IFERROR(VLOOKUP(K32, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M32" s="7">
-        <f>IFERROR(VLOOKUP(L32, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="4">
         <v>2579</v>
       </c>
@@ -6647,11 +5682,9 @@
         <f>IFERROR(VLOOKUP(K33, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>12.025</v>
       </c>
-      <c r="M33" s="7">
-        <v>45</v>
-      </c>
+      <c r="M33" s="7"/>
     </row>
-    <row r="34" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="4">
         <v>2579</v>
       </c>
@@ -6687,12 +5720,9 @@
         <f>IFERROR(VLOOKUP(K34, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M34" s="7">
-        <f>IFERROR(VLOOKUP(L34, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M34" s="7"/>
     </row>
-    <row r="35" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="8">
         <v>1650</v>
       </c>
@@ -6728,12 +5758,9 @@
         <f>IFERROR(VLOOKUP(K35, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.250</v>
       </c>
-      <c r="M35" s="11">
-        <f>IFERROR(VLOOKUP(L35, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>30</v>
-      </c>
+      <c r="M35" s="11"/>
     </row>
-    <row r="36" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="12">
         <v>2418</v>
       </c>
@@ -6769,12 +5796,9 @@
         <f>IFERROR(VLOOKUP(K36, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v>0.117</v>
       </c>
-      <c r="M36" s="15">
-        <f>IFERROR(VLOOKUP(L36, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v>28</v>
-      </c>
+      <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -6790,12 +5814,9 @@
         <f>IFERROR(VLOOKUP(K37, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M37" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L37, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M37" s="7"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -6811,12 +5832,9 @@
         <f>IFERROR(VLOOKUP(K38, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M38" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L38, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M38" s="7"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -6832,12 +5850,9 @@
         <f>IFERROR(VLOOKUP(K39, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M39" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L39, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M39" s="7"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -6853,12 +5868,9 @@
         <f>IFERROR(VLOOKUP(K40, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M40" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L40, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M40" s="7"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -6874,12 +5886,9 @@
         <f>IFERROR(VLOOKUP(K41, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M41" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L41, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M41" s="7"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -6895,12 +5904,9 @@
         <f>IFERROR(VLOOKUP(K42, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M42" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L42, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M42" s="7"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -6916,12 +5922,9 @@
         <f>IFERROR(VLOOKUP(K43, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M43" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L43, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M43" s="7"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -6937,12 +5940,9 @@
         <f>IFERROR(VLOOKUP(K44, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M44" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L44, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M44" s="7"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -6958,12 +5958,9 @@
         <f>IFERROR(VLOOKUP(K45, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M45" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L45, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M45" s="7"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -6979,12 +5976,9 @@
         <f>IFERROR(VLOOKUP(K46, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M46" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L46, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M46" s="7"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -7000,12 +5994,9 @@
         <f>IFERROR(VLOOKUP(K47, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M47" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L47, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M47" s="7"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -7021,12 +6012,9 @@
         <f>IFERROR(VLOOKUP(K48, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M48" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L48, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M48" s="7"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -7042,12 +6030,9 @@
         <f>IFERROR(VLOOKUP(K49, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M49" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L49, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M49" s="7"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -7063,12 +6048,9 @@
         <f>IFERROR(VLOOKUP(K50, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M50" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L50, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M50" s="7"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -7084,12 +6066,9 @@
         <f>IFERROR(VLOOKUP(K51, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M51" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L51, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M51" s="7"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -7105,12 +6084,9 @@
         <f>IFERROR(VLOOKUP(K52, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M52" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L52, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M52" s="7"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -7126,12 +6102,9 @@
         <f>IFERROR(VLOOKUP(K53, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M53" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L53, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M53" s="7"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -7147,12 +6120,9 @@
         <f>IFERROR(VLOOKUP(K54, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M54" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L54, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M54" s="7"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -7168,12 +6138,9 @@
         <f>IFERROR(VLOOKUP(K55, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M55" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L55, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M55" s="7"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -7189,12 +6156,9 @@
         <f>IFERROR(VLOOKUP(K56, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M56" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L56, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M56" s="7"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -7210,12 +6174,9 @@
         <f>IFERROR(VLOOKUP(K57, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M57" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L57, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M57" s="7"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -7231,12 +6192,9 @@
         <f>IFERROR(VLOOKUP(K58, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M58" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L58, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M58" s="7"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -7252,12 +6210,9 @@
         <f>IFERROR(VLOOKUP(K59, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M59" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L59, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M59" s="7"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -7273,12 +6228,9 @@
         <f>IFERROR(VLOOKUP(K60, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M60" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L60, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M60" s="7"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -7294,12 +6246,9 @@
         <f>IFERROR(VLOOKUP(K61, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M61" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L61, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M61" s="7"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -7315,10 +6264,7 @@
         <f>IFERROR(VLOOKUP(K62, [1]Conceptos!A:B, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="M62" s="7" t="str">
-        <f>IFERROR(VLOOKUP(L62, [1]Conceptos!B:C, 2, FALSE), "")</f>
-        <v/>
-      </c>
+      <c r="M62" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
